--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/203.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/203.xlsx
@@ -426,13 +426,13 @@
         <v>-2.941155645476873</v>
       </c>
       <c r="E2">
-        <v>-18.54861802670336</v>
+        <v>-15.5154144370477</v>
       </c>
       <c r="F2">
-        <v>-3.828249568873852</v>
+        <v>-4.350378654899812</v>
       </c>
       <c r="G2">
-        <v>-10.17033472295443</v>
+        <v>-8.277232361777591</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.673239927113012</v>
       </c>
       <c r="E3">
-        <v>-18.84770562101396</v>
+        <v>-15.89312992555348</v>
       </c>
       <c r="F3">
-        <v>-3.522911687467149</v>
+        <v>-4.242116833925736</v>
       </c>
       <c r="G3">
-        <v>-10.35221609488199</v>
+        <v>-6.93296217173775</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.354537803625628</v>
       </c>
       <c r="E4">
-        <v>-20.27466400862295</v>
+        <v>-16.05899887150643</v>
       </c>
       <c r="F4">
-        <v>-3.471185113366737</v>
+        <v>-4.552166469119562</v>
       </c>
       <c r="G4">
-        <v>-9.876705886348768</v>
+        <v>-7.019470037224446</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.001260706848896</v>
       </c>
       <c r="E5">
-        <v>-20.14296692753188</v>
+        <v>-17.53201183977343</v>
       </c>
       <c r="F5">
-        <v>-3.500159748381857</v>
+        <v>-4.304090312798778</v>
       </c>
       <c r="G5">
-        <v>-9.771384190562395</v>
+        <v>-6.981978108992199</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.606387872370442</v>
       </c>
       <c r="E6">
-        <v>-20.5306269449585</v>
+        <v>-17.27116720845761</v>
       </c>
       <c r="F6">
-        <v>-3.782975976841248</v>
+        <v>-4.115666549888391</v>
       </c>
       <c r="G6">
-        <v>-9.42554805080243</v>
+        <v>-6.794399288191554</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.171756599377666</v>
       </c>
       <c r="E7">
-        <v>-21.03393513159301</v>
+        <v>-18.23891116084478</v>
       </c>
       <c r="F7">
-        <v>-3.596677804686445</v>
+        <v>-4.228286411768595</v>
       </c>
       <c r="G7">
-        <v>-9.718418772479595</v>
+        <v>-6.771265195963128</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.6947387558254418</v>
       </c>
       <c r="E8">
-        <v>-22.38329811708057</v>
+        <v>-18.27537443355454</v>
       </c>
       <c r="F8">
-        <v>-3.688944679479865</v>
+        <v>-4.382870537907219</v>
       </c>
       <c r="G8">
-        <v>-8.961935942937354</v>
+        <v>-5.219609191161183</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.1857861869312667</v>
       </c>
       <c r="E9">
-        <v>-22.05920881777362</v>
+        <v>-18.4561284735707</v>
       </c>
       <c r="F9">
-        <v>-3.862384932808414</v>
+        <v>-4.252547636261787</v>
       </c>
       <c r="G9">
-        <v>-9.29186491138112</v>
+        <v>-6.114932990074919</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.3536677559314986</v>
       </c>
       <c r="E10">
-        <v>-22.88800560218344</v>
+        <v>-20.13149630287045</v>
       </c>
       <c r="F10">
-        <v>-3.626940551012919</v>
+        <v>-4.323109628367054</v>
       </c>
       <c r="G10">
-        <v>-7.956367667020348</v>
+        <v>-4.730704515376075</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.9107924415680757</v>
       </c>
       <c r="E11">
-        <v>-23.28131715517164</v>
+        <v>-20.98773111129275</v>
       </c>
       <c r="F11">
-        <v>-4.171233435268181</v>
+        <v>-4.352876182619251</v>
       </c>
       <c r="G11">
-        <v>-8.235542661801549</v>
+        <v>-4.841273425842193</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.470188774686091</v>
       </c>
       <c r="E12">
-        <v>-23.78504196141485</v>
+        <v>-21.533398643795</v>
       </c>
       <c r="F12">
-        <v>-3.631860225018146</v>
+        <v>-4.416004405651797</v>
       </c>
       <c r="G12">
-        <v>-6.338884774715535</v>
+        <v>-4.519422188514248</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.019940602823994</v>
       </c>
       <c r="E13">
-        <v>-25.50857916873419</v>
+        <v>-21.54990040307895</v>
       </c>
       <c r="F13">
-        <v>-3.538931484669888</v>
+        <v>-4.397260108061249</v>
       </c>
       <c r="G13">
-        <v>-6.935752961627355</v>
+        <v>-4.26654285695148</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.538069404494499</v>
       </c>
       <c r="E14">
-        <v>-24.68988540983548</v>
+        <v>-22.02513657933991</v>
       </c>
       <c r="F14">
-        <v>-3.796682972255371</v>
+        <v>-4.064542198889814</v>
       </c>
       <c r="G14">
-        <v>-5.738957643725429</v>
+        <v>-3.700777245381112</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.010605703588775</v>
       </c>
       <c r="E15">
-        <v>-27.06355298806601</v>
+        <v>-23.81283773487393</v>
       </c>
       <c r="F15">
-        <v>-3.654127569172799</v>
+        <v>-3.937242009897197</v>
       </c>
       <c r="G15">
-        <v>-6.442557818823352</v>
+        <v>-3.627173886406496</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.426367071102932</v>
       </c>
       <c r="E16">
-        <v>-25.76951436953016</v>
+        <v>-23.61113044562428</v>
       </c>
       <c r="F16">
-        <v>-3.183676183570487</v>
+        <v>-4.017032843237054</v>
       </c>
       <c r="G16">
-        <v>-5.218808039140679</v>
+        <v>-2.490852303870436</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.773357165333015</v>
       </c>
       <c r="E17">
-        <v>-27.75113836749465</v>
+        <v>-24.83344256435264</v>
       </c>
       <c r="F17">
-        <v>-3.209354744689869</v>
+        <v>-3.691835681715635</v>
       </c>
       <c r="G17">
-        <v>-4.419033205581389</v>
+        <v>-2.714711393235953</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.049700565452806</v>
       </c>
       <c r="E18">
-        <v>-27.98204525714576</v>
+        <v>-25.98557692138413</v>
       </c>
       <c r="F18">
-        <v>-3.404086525372574</v>
+        <v>-3.873511563762817</v>
       </c>
       <c r="G18">
-        <v>-5.572420650372392</v>
+        <v>-2.107514304241607</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.252081603937961</v>
       </c>
       <c r="E19">
-        <v>-28.78241228173543</v>
+        <v>-26.26654156271603</v>
       </c>
       <c r="F19">
-        <v>-2.943561466358008</v>
+        <v>-3.381042172594094</v>
       </c>
       <c r="G19">
-        <v>-4.783411710906812</v>
+        <v>-2.485479288460199</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.378967598256422</v>
       </c>
       <c r="E20">
-        <v>-28.69109107489675</v>
+        <v>-26.79935275751051</v>
       </c>
       <c r="F20">
-        <v>-3.028908988235844</v>
+        <v>-3.402400797707877</v>
       </c>
       <c r="G20">
-        <v>-4.403589510640689</v>
+        <v>-1.192833745559753</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.428848447219326</v>
       </c>
       <c r="E21">
-        <v>-29.74985282636408</v>
+        <v>-26.98403298449132</v>
       </c>
       <c r="F21">
-        <v>-2.440447554063311</v>
+        <v>-3.177598451936147</v>
       </c>
       <c r="G21">
-        <v>-3.972179079236103</v>
+        <v>-1.979296875505634</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.39772224211646</v>
       </c>
       <c r="E22">
-        <v>-30.1989121586237</v>
+        <v>-27.88456079718264</v>
       </c>
       <c r="F22">
-        <v>-3.085220575910752</v>
+        <v>-2.905555969917567</v>
       </c>
       <c r="G22">
-        <v>-5.011958532755937</v>
+        <v>-1.658339485473292</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.277846918539305</v>
       </c>
       <c r="E23">
-        <v>-31.67881293585637</v>
+        <v>-27.97348191279726</v>
       </c>
       <c r="F23">
-        <v>-2.951078072171011</v>
+        <v>-2.783747028438108</v>
       </c>
       <c r="G23">
-        <v>-3.940546816608367</v>
+        <v>-1.797408882486996</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.059741159007752</v>
       </c>
       <c r="E24">
-        <v>-30.28032053585959</v>
+        <v>-28.75445348321207</v>
       </c>
       <c r="F24">
-        <v>-3.033029287697369</v>
+        <v>-2.679371078950564</v>
       </c>
       <c r="G24">
-        <v>-4.089163826957329</v>
+        <v>-1.832454317565721</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.738177323912878</v>
       </c>
       <c r="E25">
-        <v>-30.78786284569127</v>
+        <v>-28.08581523903153</v>
       </c>
       <c r="F25">
-        <v>-2.625718550638644</v>
+        <v>-2.698654643720334</v>
       </c>
       <c r="G25">
-        <v>-4.391131927776411</v>
+        <v>-1.983517821068205</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.304988978668683</v>
       </c>
       <c r="E26">
-        <v>-31.87538267134432</v>
+        <v>-28.10328156327911</v>
       </c>
       <c r="F26">
-        <v>-2.959658301729208</v>
+        <v>-2.622306505306512</v>
       </c>
       <c r="G26">
-        <v>-3.73766996487075</v>
+        <v>-1.906812480923292</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.76382922456332</v>
       </c>
       <c r="E27">
-        <v>-31.69978656322289</v>
+        <v>-28.28295329800744</v>
       </c>
       <c r="F27">
-        <v>-2.683344757381794</v>
+        <v>-2.296467359047924</v>
       </c>
       <c r="G27">
-        <v>-4.046633248414312</v>
+        <v>-2.838449653857293</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.124951837951801</v>
       </c>
       <c r="E28">
-        <v>-31.64139641936799</v>
+        <v>-28.96025904143866</v>
       </c>
       <c r="F28">
-        <v>-2.559974343348058</v>
+        <v>-2.646894106556407</v>
       </c>
       <c r="G28">
-        <v>-4.829914944096954</v>
+        <v>-2.582938438590803</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.400461959889548</v>
       </c>
       <c r="E29">
-        <v>-32.61808410792031</v>
+        <v>-29.00154061049259</v>
       </c>
       <c r="F29">
-        <v>-2.609452728317272</v>
+        <v>-2.573724413867127</v>
       </c>
       <c r="G29">
-        <v>-4.6738127902837</v>
+        <v>-2.812392349917689</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.620080358622768</v>
       </c>
       <c r="E30">
-        <v>-32.2519773625332</v>
+        <v>-28.10964406925989</v>
       </c>
       <c r="F30">
-        <v>-2.291792881793926</v>
+        <v>-2.662093820030375</v>
       </c>
       <c r="G30">
-        <v>-5.089014790728013</v>
+        <v>-3.129416811849377</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1903012440983274</v>
       </c>
       <c r="E31">
-        <v>-31.21742256887386</v>
+        <v>-28.34217215260574</v>
       </c>
       <c r="F31">
-        <v>-2.443177024655536</v>
+        <v>-2.791624802438731</v>
       </c>
       <c r="G31">
-        <v>-5.7545337604877</v>
+        <v>-2.632695938046049</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.999078194278304</v>
       </c>
       <c r="E32">
-        <v>-30.05801321834905</v>
+        <v>-27.86522421316989</v>
       </c>
       <c r="F32">
-        <v>-2.65714183969644</v>
+        <v>-2.570118530562741</v>
       </c>
       <c r="G32">
-        <v>-4.756655881858421</v>
+        <v>-2.945532559870558</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.769366657127744</v>
       </c>
       <c r="E33">
-        <v>-30.58155462684983</v>
+        <v>-27.47822535294839</v>
       </c>
       <c r="F33">
-        <v>-2.971998490928712</v>
+        <v>-2.440059878118801</v>
       </c>
       <c r="G33">
-        <v>-4.541251925800203</v>
+        <v>-3.284684708186735</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.476712447276943</v>
       </c>
       <c r="E34">
-        <v>-30.81641713854664</v>
+        <v>-26.55060820874318</v>
       </c>
       <c r="F34">
-        <v>-2.613975614336558</v>
+        <v>-2.644387466795536</v>
       </c>
       <c r="G34">
-        <v>-4.77505920451123</v>
+        <v>-3.32767545255971</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.091710110376071</v>
       </c>
       <c r="E35">
-        <v>-29.95907058975546</v>
+        <v>-26.72368648531635</v>
       </c>
       <c r="F35">
-        <v>-2.287575663346274</v>
+        <v>-2.417903535196123</v>
       </c>
       <c r="G35">
-        <v>-5.985447622397404</v>
+        <v>-2.968438224456776</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.59291253056213</v>
       </c>
       <c r="E36">
-        <v>-28.05969500095528</v>
+        <v>-25.09244410674734</v>
       </c>
       <c r="F36">
-        <v>-2.254982719515725</v>
+        <v>-2.58281243264324</v>
       </c>
       <c r="G36">
-        <v>-5.211147436762806</v>
+        <v>-3.569679642025973</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.969873354671371</v>
       </c>
       <c r="E37">
-        <v>-29.84449114041338</v>
+        <v>-25.6553560682708</v>
       </c>
       <c r="F37">
-        <v>-2.437239287112269</v>
+        <v>-2.571042160216862</v>
       </c>
       <c r="G37">
-        <v>-5.377343443925298</v>
+        <v>-4.064059960133036</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.212678859648282</v>
       </c>
       <c r="E38">
-        <v>-26.5458940673012</v>
+        <v>-24.9705104156168</v>
       </c>
       <c r="F38">
-        <v>-2.154061890465258</v>
+        <v>-2.369894673999475</v>
       </c>
       <c r="G38">
-        <v>-6.554868076243127</v>
+        <v>-4.354672889752417</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.326640709268044</v>
       </c>
       <c r="E39">
-        <v>-27.57271196311843</v>
+        <v>-24.90006094547948</v>
       </c>
       <c r="F39">
-        <v>-2.394396953406881</v>
+        <v>-2.543816208789051</v>
       </c>
       <c r="G39">
-        <v>-6.00313586721373</v>
+        <v>-3.373043168629883</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.323132966514773</v>
       </c>
       <c r="E40">
-        <v>-26.04675207675375</v>
+        <v>-23.87337437540847</v>
       </c>
       <c r="F40">
-        <v>-2.136894804409641</v>
+        <v>-2.551190335408772</v>
       </c>
       <c r="G40">
-        <v>-5.87926849531636</v>
+        <v>-3.710208989622496</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.217713298961554</v>
       </c>
       <c r="E41">
-        <v>-24.97572721767364</v>
+        <v>-23.30620111984379</v>
       </c>
       <c r="F41">
-        <v>-2.198773021031362</v>
+        <v>-2.062226595088696</v>
       </c>
       <c r="G41">
-        <v>-6.653542196586645</v>
+        <v>-2.706137080289241</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.034466494413291</v>
       </c>
       <c r="E42">
-        <v>-25.40299326877135</v>
+        <v>-22.97338545112406</v>
       </c>
       <c r="F42">
-        <v>-1.919398659130603</v>
+        <v>-1.768452722625074</v>
       </c>
       <c r="G42">
-        <v>-6.356781583900836</v>
+        <v>-3.54693619417118</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.797718498245802</v>
       </c>
       <c r="E43">
-        <v>-26.21824085895022</v>
+        <v>-22.15634005676414</v>
       </c>
       <c r="F43">
-        <v>-2.502474876817536</v>
+        <v>-1.973505132779258</v>
       </c>
       <c r="G43">
-        <v>-7.365501499171227</v>
+        <v>-3.951623901982769</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.532504574178371</v>
       </c>
       <c r="E44">
-        <v>-25.30560390676239</v>
+        <v>-21.98932993536126</v>
       </c>
       <c r="F44">
-        <v>-2.095184020576478</v>
+        <v>-1.827268464958645</v>
       </c>
       <c r="G44">
-        <v>-6.219615750572212</v>
+        <v>-3.372947162809244</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.263724771221802</v>
       </c>
       <c r="E45">
-        <v>-22.98630518746794</v>
+        <v>-21.00378455164994</v>
       </c>
       <c r="F45">
-        <v>-1.589166680534969</v>
+        <v>-2.296406059860117</v>
       </c>
       <c r="G45">
-        <v>-7.002453833152591</v>
+        <v>-3.926536587886171</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.012798471249397</v>
       </c>
       <c r="E46">
-        <v>-23.31914349855771</v>
+        <v>-20.07794709772975</v>
       </c>
       <c r="F46">
-        <v>-1.53352358535412</v>
+        <v>-2.11094122531253</v>
       </c>
       <c r="G46">
-        <v>-6.255611312220708</v>
+        <v>-3.877868257913346</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.795250757148864</v>
       </c>
       <c r="E47">
-        <v>-23.1148640360717</v>
+        <v>-19.50629065289748</v>
       </c>
       <c r="F47">
-        <v>-1.873141794990876</v>
+        <v>-2.041663202681602</v>
       </c>
       <c r="G47">
-        <v>-6.059441625745655</v>
+        <v>-4.054436204250375</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.623188312064029</v>
       </c>
       <c r="E48">
-        <v>-22.48660166614355</v>
+        <v>-19.56286035020129</v>
       </c>
       <c r="F48">
-        <v>-1.360634196348433</v>
+        <v>-1.843936873837776</v>
       </c>
       <c r="G48">
-        <v>-7.065943475504734</v>
+        <v>-4.608187846058727</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.501164707583071</v>
       </c>
       <c r="E49">
-        <v>-22.28125801226573</v>
+        <v>-18.3395836665093</v>
       </c>
       <c r="F49">
-        <v>-1.414937821438955</v>
+        <v>-1.764435140721497</v>
       </c>
       <c r="G49">
-        <v>-6.700641327973855</v>
+        <v>-4.073438735645791</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.427942779929426</v>
       </c>
       <c r="E50">
-        <v>-20.45138317829828</v>
+        <v>-18.27593143585748</v>
       </c>
       <c r="F50">
-        <v>-1.854067807174014</v>
+        <v>-1.787636054939105</v>
       </c>
       <c r="G50">
-        <v>-7.310622585766729</v>
+        <v>-4.514655002937698</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.401107780818562</v>
       </c>
       <c r="E51">
-        <v>-20.14255936487119</v>
+        <v>-17.23053773966079</v>
       </c>
       <c r="F51">
-        <v>-1.437615207457994</v>
+        <v>-1.879794413602759</v>
       </c>
       <c r="G51">
-        <v>-7.753513989101506</v>
+        <v>-3.934915578646067</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.411491491084877</v>
       </c>
       <c r="E52">
-        <v>-19.19056091660869</v>
+        <v>-17.09237399768677</v>
       </c>
       <c r="F52">
-        <v>-1.338546607920187</v>
+        <v>-1.587138008765513</v>
       </c>
       <c r="G52">
-        <v>-6.694152658716884</v>
+        <v>-4.760717921235107</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.44932230477389</v>
       </c>
       <c r="E53">
-        <v>-19.40084513562887</v>
+        <v>-16.12736524360023</v>
       </c>
       <c r="F53">
-        <v>-1.309335888195268</v>
+        <v>-2.167407717691761</v>
       </c>
       <c r="G53">
-        <v>-7.667856933818403</v>
+        <v>-4.648245447083908</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.505364437661643</v>
       </c>
       <c r="E54">
-        <v>-19.49702539507778</v>
+        <v>-16.34363157678454</v>
       </c>
       <c r="F54">
-        <v>-1.723915549213559</v>
+        <v>-1.705323671225127</v>
       </c>
       <c r="G54">
-        <v>-7.816904315087471</v>
+        <v>-5.22085064573841</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.569116284434779</v>
       </c>
       <c r="E55">
-        <v>-18.01004661297113</v>
+        <v>-16.39291495941002</v>
       </c>
       <c r="F55">
-        <v>-1.522204773162268</v>
+        <v>-1.720946680441926</v>
       </c>
       <c r="G55">
-        <v>-7.148329711795038</v>
+        <v>-4.738845146857143</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.633495981949907</v>
       </c>
       <c r="E56">
-        <v>-18.20416417978392</v>
+        <v>-15.83879276593544</v>
       </c>
       <c r="F56">
-        <v>-1.616662679736093</v>
+        <v>-2.005688034745422</v>
       </c>
       <c r="G56">
-        <v>-8.02445565712654</v>
+        <v>-5.029603740480252</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.690821130768597</v>
       </c>
       <c r="E57">
-        <v>-17.70765323263493</v>
+        <v>-15.81917541653422</v>
       </c>
       <c r="F57">
-        <v>-1.346493964782645</v>
+        <v>-1.899157501643197</v>
       </c>
       <c r="G57">
-        <v>-7.02612754430392</v>
+        <v>-5.189013129287239</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.735597764791917</v>
       </c>
       <c r="E58">
-        <v>-17.7940067034872</v>
+        <v>-14.87912308270395</v>
       </c>
       <c r="F58">
-        <v>-1.741544035912535</v>
+        <v>-1.723076413034523</v>
       </c>
       <c r="G58">
-        <v>-8.048884172660822</v>
+        <v>-4.478894490022491</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.765256256223536</v>
       </c>
       <c r="E59">
-        <v>-17.49797582913178</v>
+        <v>-14.19827607259873</v>
       </c>
       <c r="F59">
-        <v>-1.696026903863508</v>
+        <v>-1.615086296568566</v>
       </c>
       <c r="G59">
-        <v>-8.483962688522919</v>
+        <v>-5.24160776626964</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.776100080593658</v>
       </c>
       <c r="E60">
-        <v>-17.46670671610881</v>
+        <v>-14.08752318379313</v>
       </c>
       <c r="F60">
-        <v>-1.943751004038103</v>
+        <v>-1.760170705331885</v>
       </c>
       <c r="G60">
-        <v>-8.449698542191463</v>
+        <v>-5.84238570746334</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.766224983282307</v>
       </c>
       <c r="E61">
-        <v>-16.13850076118509</v>
+        <v>-14.05478231671768</v>
       </c>
       <c r="F61">
-        <v>-1.570671721532664</v>
+        <v>-1.605252747129932</v>
       </c>
       <c r="G61">
-        <v>-8.461540363585435</v>
+        <v>-5.98696716279993</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.73483474671739</v>
       </c>
       <c r="E62">
-        <v>-17.16452617405098</v>
+        <v>-13.50649732623899</v>
       </c>
       <c r="F62">
-        <v>-1.369005677321125</v>
+        <v>-1.88850304010839</v>
       </c>
       <c r="G62">
-        <v>-7.521924775901791</v>
+        <v>-5.698989427429808</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.68010374670768</v>
       </c>
       <c r="E63">
-        <v>-15.8543526026258</v>
+        <v>-13.68183983981598</v>
       </c>
       <c r="F63">
-        <v>-1.872585132096195</v>
+        <v>-2.002035762866479</v>
       </c>
       <c r="G63">
-        <v>-8.198520831035879</v>
+        <v>-5.709295155693559</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.601344251852727</v>
       </c>
       <c r="E64">
-        <v>-16.29648563389069</v>
+        <v>-12.56442076452729</v>
       </c>
       <c r="F64">
-        <v>-1.815738419079078</v>
+        <v>-1.74311379214084</v>
       </c>
       <c r="G64">
-        <v>-9.064605891746771</v>
+        <v>-5.447232370804852</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.49774008255467</v>
       </c>
       <c r="E65">
-        <v>-16.18316057184874</v>
+        <v>-13.31347112166204</v>
       </c>
       <c r="F65">
-        <v>-2.013656929160353</v>
+        <v>-2.231534123444679</v>
       </c>
       <c r="G65">
-        <v>-8.678503586592651</v>
+        <v>-5.712483211047878</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.367163716606997</v>
       </c>
       <c r="E66">
-        <v>-15.41459702021494</v>
+        <v>-12.79900477507263</v>
       </c>
       <c r="F66">
-        <v>-1.882552048686678</v>
+        <v>-1.876821402994111</v>
       </c>
       <c r="G66">
-        <v>-8.809001981205181</v>
+        <v>-6.308603214667822</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.211585174014079</v>
       </c>
       <c r="E67">
-        <v>-15.70408877810328</v>
+        <v>-12.2301469271771</v>
       </c>
       <c r="F67">
-        <v>-1.866702066801512</v>
+        <v>-1.87544796984027</v>
       </c>
       <c r="G67">
-        <v>-8.680026437540716</v>
+        <v>-6.540642662060879</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.031775320299167</v>
       </c>
       <c r="E68">
-        <v>-15.24209838831476</v>
+        <v>-12.10648335897564</v>
       </c>
       <c r="F68">
-        <v>-2.180503377962618</v>
+        <v>-2.084739964361982</v>
       </c>
       <c r="G68">
-        <v>-9.626845772317814</v>
+        <v>-6.189112383973367</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.829326829025919</v>
       </c>
       <c r="E69">
-        <v>-14.62483568175124</v>
+        <v>-12.42618003849514</v>
       </c>
       <c r="F69">
-        <v>-2.060784407440423</v>
+        <v>-1.974601891220565</v>
       </c>
       <c r="G69">
-        <v>-8.181948240066287</v>
+        <v>-5.474726451508499</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.609443777877409</v>
       </c>
       <c r="E70">
-        <v>-14.89466027702427</v>
+        <v>-12.21557429782041</v>
       </c>
       <c r="F70">
-        <v>-2.055366056258711</v>
+        <v>-2.082244093377347</v>
       </c>
       <c r="G70">
-        <v>-7.598116981488117</v>
+        <v>-5.952206434637582</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.373139470880388</v>
       </c>
       <c r="E71">
-        <v>-14.01415737639486</v>
+        <v>-12.71578047975967</v>
       </c>
       <c r="F71">
-        <v>-1.975021045126381</v>
+        <v>-2.072067599833955</v>
       </c>
       <c r="G71">
-        <v>-8.818791264364807</v>
+        <v>-5.781819276822373</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.123965542030805</v>
       </c>
       <c r="E72">
-        <v>-14.53658025181575</v>
+        <v>-11.89275297123562</v>
       </c>
       <c r="F72">
-        <v>-2.467787820192709</v>
+        <v>-1.996135301856338</v>
       </c>
       <c r="G72">
-        <v>-8.037926266925833</v>
+        <v>-5.630970958779942</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.8659425240784033</v>
       </c>
       <c r="E73">
-        <v>-16.10791544773729</v>
+        <v>-11.99360661586044</v>
       </c>
       <c r="F73">
-        <v>-2.15739441252672</v>
+        <v>-2.100039081924286</v>
       </c>
       <c r="G73">
-        <v>-8.935762769903876</v>
+        <v>-5.771424163829061</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.5991183031736147</v>
       </c>
       <c r="E74">
-        <v>-15.83262045586299</v>
+        <v>-13.26022985275386</v>
       </c>
       <c r="F74">
-        <v>-1.955204011749209</v>
+        <v>-2.536067660103264</v>
       </c>
       <c r="G74">
-        <v>-8.219390510115444</v>
+        <v>-5.858527927512826</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.3290877220405662</v>
       </c>
       <c r="E75">
-        <v>-16.30969066409705</v>
+        <v>-13.62607168241152</v>
       </c>
       <c r="F75">
-        <v>-2.203654590136059</v>
+        <v>-2.527257972774491</v>
       </c>
       <c r="G75">
-        <v>-8.334428657059579</v>
+        <v>-5.675378616643726</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.05886943737574774</v>
       </c>
       <c r="E76">
-        <v>-17.75141640544506</v>
+        <v>-13.13192912716854</v>
       </c>
       <c r="F76">
-        <v>-2.224656188899235</v>
+        <v>-2.135595924322052</v>
       </c>
       <c r="G76">
-        <v>-8.374009539527105</v>
+        <v>-5.628339075076221</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.208678857634546</v>
       </c>
       <c r="E77">
-        <v>-16.66504454795296</v>
+        <v>-13.91080854259181</v>
       </c>
       <c r="F77">
-        <v>-2.485081646460955</v>
+        <v>-2.638509371705271</v>
       </c>
       <c r="G77">
-        <v>-7.694063212307275</v>
+        <v>-5.414454659420528</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.4662634410218422</v>
       </c>
       <c r="E78">
-        <v>-16.98022633888681</v>
+        <v>-14.03748807448238</v>
       </c>
       <c r="F78">
-        <v>-2.076345289102012</v>
+        <v>-2.306953661999963</v>
       </c>
       <c r="G78">
-        <v>-8.109119548747861</v>
+        <v>-5.105054383865782</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.7112694247416854</v>
       </c>
       <c r="E79">
-        <v>-17.63533803120644</v>
+        <v>-14.66597686811092</v>
       </c>
       <c r="F79">
-        <v>-2.748750990772037</v>
+        <v>-2.562537312092319</v>
       </c>
       <c r="G79">
-        <v>-7.16725610064305</v>
+        <v>-5.535392198515644</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.9383232977779766</v>
       </c>
       <c r="E80">
-        <v>-17.84470297000307</v>
+        <v>-15.00220247775842</v>
       </c>
       <c r="F80">
-        <v>-2.582515877113038</v>
+        <v>-2.780175108197236</v>
       </c>
       <c r="G80">
-        <v>-6.774767753143676</v>
+        <v>-5.100853301576447</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.141486323469927</v>
       </c>
       <c r="E81">
-        <v>-18.01828843566509</v>
+        <v>-15.98563306410816</v>
       </c>
       <c r="F81">
-        <v>-2.759954659894901</v>
+        <v>-3.020141547644614</v>
       </c>
       <c r="G81">
-        <v>-7.94341350232518</v>
+        <v>-4.546313749929748</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.31774139947506</v>
       </c>
       <c r="E82">
-        <v>-19.58977759970288</v>
+        <v>-16.781969746831</v>
       </c>
       <c r="F82">
-        <v>-2.982037475483239</v>
+        <v>-2.887630927688388</v>
       </c>
       <c r="G82">
-        <v>-6.653946083142436</v>
+        <v>-5.007019198811345</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.460876801849363</v>
       </c>
       <c r="E83">
-        <v>-19.02082012537918</v>
+        <v>-16.66768917677343</v>
       </c>
       <c r="F83">
-        <v>-2.675737031154483</v>
+        <v>-2.860072800932055</v>
       </c>
       <c r="G83">
-        <v>-7.58465961387098</v>
+        <v>-4.624475730111941</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.56709224973963</v>
       </c>
       <c r="E84">
-        <v>-22.23765786451988</v>
+        <v>-17.90708269945873</v>
       </c>
       <c r="F84">
-        <v>-3.167616624732413</v>
+        <v>-2.985439580406537</v>
       </c>
       <c r="G84">
-        <v>-7.902008509265515</v>
+        <v>-4.633722083803125</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.632319493393231</v>
       </c>
       <c r="E85">
-        <v>-21.76485800727505</v>
+        <v>-18.57227477491943</v>
       </c>
       <c r="F85">
-        <v>-3.164865616587716</v>
+        <v>-3.13201339376009</v>
       </c>
       <c r="G85">
-        <v>-6.547713987332762</v>
+        <v>-4.149634251777656</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.65275374388917</v>
       </c>
       <c r="E86">
-        <v>-22.82160911628298</v>
+        <v>-20.23988079977003</v>
       </c>
       <c r="F86">
-        <v>-3.388198438586879</v>
+        <v>-3.325692319473837</v>
       </c>
       <c r="G86">
-        <v>-5.757056396188625</v>
+        <v>-3.773377509057329</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.625757328063022</v>
       </c>
       <c r="E87">
-        <v>-23.0475573268957</v>
+        <v>-20.48376176745312</v>
       </c>
       <c r="F87">
-        <v>-3.519170780276106</v>
+        <v>-3.536884588817571</v>
       </c>
       <c r="G87">
-        <v>-6.48899153055717</v>
+        <v>-3.908957591072642</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.549995353606772</v>
       </c>
       <c r="E88">
-        <v>-24.25949471167248</v>
+        <v>-21.26799383915346</v>
       </c>
       <c r="F88">
-        <v>-3.661778370505055</v>
+        <v>-3.532398150964009</v>
       </c>
       <c r="G88">
-        <v>-6.793836495449878</v>
+        <v>-4.298535969042996</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.426788402594516</v>
       </c>
       <c r="E89">
-        <v>-26.28187950418001</v>
+        <v>-22.49550011756862</v>
       </c>
       <c r="F89">
-        <v>-3.37907894184946</v>
+        <v>-3.623933577340757</v>
       </c>
       <c r="G89">
-        <v>-6.228504565345156</v>
+        <v>-3.949230377557876</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.257747177136471</v>
       </c>
       <c r="E90">
-        <v>-26.60252263476712</v>
+        <v>-25.22980178034799</v>
       </c>
       <c r="F90">
-        <v>-3.992957173042089</v>
+        <v>-3.869146895917467</v>
       </c>
       <c r="G90">
-        <v>-5.673822660240268</v>
+        <v>-4.00507928080538</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.048446318030779</v>
       </c>
       <c r="E91">
-        <v>-28.24740477704723</v>
+        <v>-25.77570026502464</v>
       </c>
       <c r="F91">
-        <v>-3.412379311442</v>
+        <v>-4.37635211481459</v>
       </c>
       <c r="G91">
-        <v>-5.307596870503932</v>
+        <v>-3.380832882283788</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.8041492366300327</v>
       </c>
       <c r="E92">
-        <v>-30.16408140079371</v>
+        <v>-27.69037983173374</v>
       </c>
       <c r="F92">
-        <v>-3.4424722424509</v>
+        <v>-4.045718378028598</v>
       </c>
       <c r="G92">
-        <v>-5.955745407819063</v>
+        <v>-3.943460096682926</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.5297265356041831</v>
       </c>
       <c r="E93">
-        <v>-31.24239257455216</v>
+        <v>-30.33703514433166</v>
       </c>
       <c r="F93">
-        <v>-4.356139121818879</v>
+        <v>-4.611037712069121</v>
       </c>
       <c r="G93">
-        <v>-5.53577291125266</v>
+        <v>-3.716896291611823</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.2343019477460058</v>
       </c>
       <c r="E94">
-        <v>-33.85350615890088</v>
+        <v>-31.68134888130066</v>
       </c>
       <c r="F94">
-        <v>-4.673933163861479</v>
+        <v>-4.525523688343322</v>
       </c>
       <c r="G94">
-        <v>-6.655068358080248</v>
+        <v>-3.528009805323167</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.07733126347069827</v>
       </c>
       <c r="E95">
-        <v>-35.71349081654533</v>
+        <v>-33.50955044412228</v>
       </c>
       <c r="F95">
-        <v>-4.435664049222437</v>
+        <v>-4.908626216422634</v>
       </c>
       <c r="G95">
-        <v>-6.475974465496756</v>
+        <v>-4.139553640610576</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.4000767796801417</v>
       </c>
       <c r="E96">
-        <v>-38.17640782475603</v>
+        <v>-35.22832822525956</v>
       </c>
       <c r="F96">
-        <v>-4.827075930719231</v>
+        <v>-5.091588553046364</v>
       </c>
       <c r="G96">
-        <v>-6.6204930204681</v>
+        <v>-4.515310490954474</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.7234328062837015</v>
       </c>
       <c r="E97">
-        <v>-39.22904934360201</v>
+        <v>-37.23711853879606</v>
       </c>
       <c r="F97">
-        <v>-4.740263026905843</v>
+        <v>-5.62751161306374</v>
       </c>
       <c r="G97">
-        <v>-6.781872183870952</v>
+        <v>-4.373586036418274</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.051407607051283</v>
       </c>
       <c r="E98">
-        <v>-41.50396675338428</v>
+        <v>-39.34120832358698</v>
       </c>
       <c r="F98">
-        <v>-6.081660728178958</v>
+        <v>-5.738962648538594</v>
       </c>
       <c r="G98">
-        <v>-7.667562295265409</v>
+        <v>-4.692173075844497</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.368456812166778</v>
       </c>
       <c r="E99">
-        <v>-41.64532986224472</v>
+        <v>-41.43622757494054</v>
       </c>
       <c r="F99">
-        <v>-5.369419666475707</v>
+        <v>-6.029105786675746</v>
       </c>
       <c r="G99">
-        <v>-7.994061538530491</v>
+        <v>-5.392704375227516</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.687973448469805</v>
       </c>
       <c r="E100">
-        <v>-44.50245279706013</v>
+        <v>-43.96576975698909</v>
       </c>
       <c r="F100">
-        <v>-5.744544188098658</v>
+        <v>-6.346843913918657</v>
       </c>
       <c r="G100">
-        <v>-8.407045473463493</v>
+        <v>-5.672038276194601</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.985279947165501</v>
       </c>
       <c r="E101">
-        <v>-46.6262935212355</v>
+        <v>-45.90411060038826</v>
       </c>
       <c r="F101">
-        <v>-6.076929921941571</v>
+        <v>-6.426495581534843</v>
       </c>
       <c r="G101">
-        <v>-7.437254263189391</v>
+        <v>-5.645411558422243</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.29698159217154</v>
       </c>
       <c r="E102">
-        <v>-48.45831145552709</v>
+        <v>-48.26198059704304</v>
       </c>
       <c r="F102">
-        <v>-6.210736936883177</v>
+        <v>-6.870167919923155</v>
       </c>
       <c r="G102">
-        <v>-8.40459898030997</v>
+        <v>-6.141450459844481</v>
       </c>
     </row>
   </sheetData>
